--- a/aq_files/0374.xlsx
+++ b/aq_files/0374.xlsx
@@ -1,195 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Sheet2" sheetId="2" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
-  <si>
-    <t>Block_ID,File_Name,File_Size_MB,Block_Size_MB,Block_Count,Replication_Factor,NameNode_ID,DataNode_ID,Rack_ID,Storage_Type,Disk_Usage_Pct,Read_Throughput_MBps,Write_Throughput_MBps,Read_Latency_Ms,Write_Latency_Ms,Metadata_Size_KB,Heartbeat_Status,Block_Location,Data_Locality_Score,Replication_Status,Corrupt_Blocks,Pending_Replication,Under_Replicated,Over_Replicated,Balancer_Score,Cluster_Health_Pct</t>
-  </si>
-  <si>
-    <t>BLK-001,user_logs_jan.parquet,1024,128,8,3,NN-01,DN-01,Rack-1,SSD,45,450,320,12,18,64,Healthy,Rack-1,92,OK,0,0,0,0,85,98</t>
-  </si>
-  <si>
-    <t>BLK-002,user_logs_jan.parquet,1024,128,8,3,NN-01,DN-05,Rack-2,HDD,62,280,210,28,35,64,Healthy,Rack-2,88,OK,0,0,0,0,85,98</t>
-  </si>
-  <si>
-    <t>BLK-003,user_logs_jan.parquet,1024,128,8,3,NN-01,DN-09,Rack-3,SSD,38,480,350,10,15,64,Healthy,Rack-3,94,OK,0,0,0,0,85,98</t>
-  </si>
-  <si>
-    <t>BLK-004,sales_transactions.avro,512,128,4,3,NN-01,DN-02,Rack-1,HDD,58,310,240,24,32,32,Healthy,Rack-1,89,OK,0,0,0,0,82,97</t>
-  </si>
-  <si>
-    <t>BLK-005,sales_transactions.avro,512,128,4,3,NN-01,DN-06,Rack-2,SSD,42,420,340,14,20,32,Healthy,Rack-2,91,OK,0,0,0,0,82,97</t>
-  </si>
-  <si>
-    <t>BLK-006,sales_transactions.avro,512,128,4,3,NN-01,DN-10,Rack-3,HDD,55,295,225,26,34,32,Healthy,Rack-3,87,OK,0,0,0,0,82,97</t>
-  </si>
-  <si>
-    <t>BLK-007,customer_data.orc,2048,128,16,3,NN-01,DN-03,Rack-1,SSD,52,510,390,9,14,128,Healthy,Rack-1,95,OK,0,0,0,0,88,99</t>
-  </si>
-  <si>
-    <t>BLK-008,customer_data.orc,2048,128,16,3,NN-01,DN-07,Rack-2,HDD,68,265,195,32,42,128,Healthy,Rack-2,84,OK,0,1,1,0,88,99</t>
-  </si>
-  <si>
-    <t>BLK-009,customer_data.orc,2048,128,16,3,NN-01,DN-11,Rack-3,SSD,48,495,380,11,16,128,Healthy,Rack-3,93,OK,0,0,0,0,88,99</t>
-  </si>
-  <si>
-    <t>BLK-010,clickstream.json,4096,128,32,3,NN-01,DN-04,Rack-1,HDD,72,235,180,38,48,256,Healthy,Rack-1,82,Under,0,2,2,0,75,94</t>
-  </si>
-  <si>
-    <t>BLK-011,clickstream.json,4096,128,32,3,NN-01,DN-08,Rack-2,SSD,48,460,360,13,19,256,Healthy,Rack-2,90,OK,0,0,0,0,75,94</t>
-  </si>
-  <si>
-    <t>BLK-012,clickstream.json,4096,128,32,3,NN-01,DN-12,Rack-3,HDD,65,275,205,30,38,256,Healthy,Rack-3,86,OK,0,0,0,0,75,94</t>
-  </si>
-  <si>
-    <t>BLK-013,product_catalog.csv,128,128,1,3,NN-01,DN-01,Rack-1,SSD,45,490,380,8,12,8,Healthy,Rack-1,96,OK,0,0,0,0,90,99</t>
-  </si>
-  <si>
-    <t>BLK-014,product_catalog.csv,128,128,1,3,NN-01,DN-05,Rack-2,HDD,62,305,235,26,33,8,Healthy,Rack-2,89,OK,0,0,0,0,90,99</t>
-  </si>
-  <si>
-    <t>BLK-015,product_catalog.csv,128,128,1,3,NN-01,DN-09,Rack-3,SSD,38,485,375,9,13,8,Healthy,Rack-3,95,OK,0,0,0,0,90,99</t>
-  </si>
-  <si>
-    <t>BLK-016,sensor_data_2024.parquet,8192,128,64,3,NN-01,DN-02,Rack-1,HDD,75,210,165,42,55,512,Healthy,Rack-1,80,Under,1,3,3,0,70,91</t>
-  </si>
-  <si>
-    <t>BLK-017,sensor_data_2024.parquet,8192,128,64,3,NN-01,DN-06,Rack-2,SSD,55,435,345,15,22,512,Healthy,Rack-2,88,OK,0,0,0,0,70,91</t>
-  </si>
-  <si>
-    <t>BLK-018,sensor_data_2024.parquet,8192,128,64,3,NN-01,DN-10,Rack-3,HDD,68,250,190,35,45,512,Healthy,Rack-3,82,OK,0,0,0,0,70,91</t>
-  </si>
-  <si>
-    <t>BLK-019,weblogs_2024.avro,3072,128,24,3,NN-01,DN-03,Rack-1,SSD,48,470,355,12,17,192,Healthy,Rack-1,92,OK,0,0,0,0,80,96</t>
-  </si>
-  <si>
-    <t>BLK-020,weblogs_2024.avro,3072,128,24,3,NN-01,DN-07,Rack-2,HDD,70,245,185,36,46,192,Healthy,Rack-2,83,OK,0,1,1,0,80,96</t>
-  </si>
-  <si>
-    <t>BLK-021,weblogs_2024.avro,3072,128,24,3,NN-01,DN-11,Rack-3,SSD,50,455,360,13,18,192,Healthy,Rack-3,91,OK,0,0,0,0,80,96</t>
-  </si>
-  <si>
-    <t>BLK-022,financial_transactions.parquet,6144,128,48,3,NN-01,DN-04,Rack-1,HDD,78,195,150,48,62,384,Healthy,Rack-1,78,Under,2,5,5,0,65,89</t>
-  </si>
-  <si>
-    <t>BLK-023,financial_transactions.parquet,6144,128,48,3,NN-01,DN-08,Rack-2,SSD,52,425,330,16,24,384,Healthy,Rack-2,87,OK,0,0,0,0,65,89</t>
-  </si>
-  <si>
-    <t>BLK-024,financial_transactions.parquet,6144,128,48,3,NN-01,DN-12,Rack-3,HDD,72,230,175,40,52,384,Healthy,Rack-3,81,OK,0,0,0,0,65,89</t>
-  </si>
-  <si>
-    <t>BLK-025,image_data.bin,5120,128,40,3,NN-01,DN-01,Rack-1,SSD,48,485,370,10,15,320,Healthy,Rack-1,94,OK,0,0,0,0,85,97</t>
-  </si>
-  <si>
-    <t>BLK-026,image_data.bin,5120,128,40,3,NN-01,DN-05,Rack-2,HDD,65,285,215,29,37,320,Healthy,Rack-2,86,OK,0,1,1,0,85,97</t>
-  </si>
-  <si>
-    <t>BLK-027,image_data.bin,5120,128,40,3,NN-01,DN-09,Rack-3,SSD,42,475,365,11,16,320,Healthy,Rack-3,93,OK,0,0,0,0,85,97</t>
-  </si>
-  <si>
-    <t>BLK-028,backup_data.parquet,10240,128,80,3,NN-01,DN-02,Rack-1,HDD,82,180,140,55,72,640,Healthy,Rack-1,75,Under,3,7,7,0,60,86</t>
-  </si>
-  <si>
-    <t>BLK-029,backup_data.parquet,10240,128,80,3,NN-01,DN-06,Rack-2,SSD,58,415,310,18,26,640,Healthy,Rack-2,85,OK,0,0,0,0,60,86</t>
-  </si>
-  <si>
-    <t>BLK-030,backup_data.parquet,10240,128,80,3,NN-01,DN-10,Rack-3,HDD,75,210,160,45,58,640,Healthy,Rack-3,79,OK,0,0,0,0,60,86</t>
-  </si>
-  <si>
-    <t>Q.No,Question,HDFS_Concept,Analysis_Required,Expected_Answer,Key_Learning</t>
-  </si>
-  <si>
-    <t>1,"What is HDFS (Hadoop Distributed File System)? Explain its core architecture using the dataset.","HDFS Architecture","Analyze NameNode, DataNode, Block structure","HDFS has NameNode (metadata) and DataNodes (data storage). Files split into 128MB blocks, replicated across DataNodes","HDFS provides distributed, fault-tolerant storage for Big Data"</t>
-  </si>
-  <si>
-    <t>2,"What is the default block size in HDFS? Why is 128MB used? Calculate total blocks from dataset.","HDFS Block Size","Analyze Block_Size_MB, Block_Count","Default block size: 128MB. Total blocks: 384 across all files. Large blocks reduce metadata overhead and improve throughput","Large block size minimizes NameNode memory usage and improves sequential I/O"</t>
-  </si>
-  <si>
-    <t>3,"What is data replication in HDFS? Why is replication factor 3 used? Calculate storage overhead.","Data Replication","Analyze Replication_Factor, File_Size_MB","Replication factor: 3. Total raw data: 34,816 MB; Actual storage: 104,448 MB (3x overhead). Provides fault tolerance","Replication ensures data durability - if one node fails, data available on 2 others"</t>
-  </si>
-  <si>
-    <t>4,"What is the role of NameNode in HDFS? Analyze NameNode metrics from the dataset.","NameNode Role","Analyze NameNode_ID, Metadata_Size_KB","NameNode (NN-01) manages metadata: stores file-to-block mapping. Metadata size: 8-640 KB per file. Tracks block locations","NameNode is the master node - stores metadata, not actual data"</t>
-  </si>
-  <si>
-    <t>5,"What is the role of DataNode in HDFS? Analyze DataNode distribution and storage types.","DataNode Role","Analyze DataNode_ID, Storage_Type, Disk_Usage_Pct","DataNodes: DN-01 to DN-12 across 3 racks. Storage: SSD (45% usage, 48% avg) and HDD (68% usage, 58% avg)","DataNodes store actual data blocks and report to NameNode"</t>
-  </si>
-  <si>
-    <t>6,"What is rack awareness in HDFS? How does it improve data locality?","Rack Awareness","Analyze Rack_ID, Data_Locality_Score","3 racks (Rack-1,2,3). Data locality scores: 92-96 for local reads, 78-84 for remote. Rack awareness reduces cross-rack traffic","Rack awareness places replicas across racks to prevent rack failure from causing data loss"</t>
-  </si>
-  <si>
-    <t>7,"What is the difference between SSD and HDD storage in HDFS? Compare performance metrics.","Storage Performance","Compare SSD vs HDD performance metrics","SSD: Read 450-510 MBps, Write 350-390 MBps, Latency 8-18ms; HDD: Read 195-310 MBps, Write 140-240 MBps, Latency 24-72ms","SSD provides 2-3x faster performance for hot data; HDD for cold storage"</t>
-  </si>
-  <si>
-    <t>8,"What is data locality? Calculate the data locality score for different file types.","Data Locality","Analyze Data_Locality_Score by file type","Customer data: 95, Product catalog: 96, User logs: 92, Sensor data: 80-88, Financial: 78-87. Larger files have lower locality","Data locality improves performance by moving computation to data"</t>
-  </si>
-  <si>
-    <t>9,"What is block corruption in HDFS? Identify files with corrupt blocks.","Block Corruption","Filter Corrupt_Blocks &gt; 0","Financial transactions: 2 corrupt blocks; Backup data: 3 corrupt blocks; Sensor data: 1 corrupt block. Total: 6 corrupt blocks","HDFS automatically detects and replicates corrupt blocks"</t>
-  </si>
-  <si>
-    <t>10,"What are under-replicated blocks? Identify files with replication issues.","Replication Management","Analyze Under_Replicated, Replication_Status","Clickstream: 2 under-replicated; Sensor data: 3; Financial: 5; Backup: 7. Total: 17 under-replicated blocks","HDFS automatically re-replicates under-replicated blocks to maintain replication factor"</t>
-  </si>
-  <si>
-    <t>11,"What is the HDFS balancer? Analyze the balancer score for different files.","Load Balancing","Analyze Balancer_Score, Disk_Usage_Pct","Balancer scores: 85-90 for balanced files; 60-70 for unbalanced. Files with high disk usage (75-82%) have lower balancer scores","Balancer redistributes data to ensure even cluster utilization"</t>
-  </si>
-  <si>
-    <t>12,"What is the relationship between file size and read throughput? Analyze performance scaling.","Performance Analysis","Correlate File_Size_MB with Read_Throughput_MBps","Small files (128MB): 490 MBps; Medium (512MB): 310-420 MBps; Large (8192MB): 210-435 MBps. Larger files have more variable performance","Performance depends on data distribution and storage type"</t>
-  </si>
-  <si>
-    <t>13,"What is the cluster health percentage? Calculate average health by storage type.","Cluster Health","Group by Storage_Type; average Cluster_Health_Pct","SSD clusters: 97.8% health; HDD clusters: 93.2% health. Overall cluster health: 95.2%","Regular monitoring and balancing maintain cluster health"</t>
-  </si>
-  <si>
-    <t>14,"What is the difference between read and write latency? Compare across storage types.","Latency Analysis","Compare Read_Latency_Ms vs Write_Latency_Ms","SSD: Read 8-16ms, Write 12-26ms; HDD: Read 24-55ms, Write 32-72ms. Write latency 30-40% higher than read","Write operations require additional overhead for replication"</t>
-  </si>
-  <si>
-    <t>15,"What is the HDFS architecture for large files? Analyze the 10GB backup file.","Large File Handling","Analyze backup_data.parquet (10,240 MB)","Blocks: 80 blocks × 128MB; Replication: 3; Storage: 30,720 MB actual; Under-replicated: 7 blocks; Health: 86%","Large files are split into many blocks distributed across cluster"</t>
-  </si>
-  <si>
-    <t>16,"What is the NameNode metadata size? Calculate metadata overhead for different file sizes.","Metadata Overhead","Analyze File_Size_MB vs Metadata_Size_KB","Small file (128MB): 8KB metadata; Large file (10GB): 640KB metadata. Overhead: ~64 bytes per block","NameNode memory limits number of files; each file/block consumes memory"</t>
-  </si>
-  <si>
-    <t>17,"What are the different storage types used in HDFS? Identify files by storage type.","Storage Tiering","Group by Storage_Type, count files","SSD: 15 files (50%): user_logs, customer_data, weblogs, product_catalog; HDD: 15 files (50%): sales, clickstream, sensor, financial, backup","Hot data on SSD, cold data on HDD for cost-performance balance"</t>
-  </si>
-  <si>
-    <t>18,"What is the replication status of files? Identify files with replication issues.","Replication Status","Analyze Replication_Status, Under_Replicated","OK: 24 files (80%); Under: 6 files (20%). Clickstream, sensor, financial, backup have under-replicated blocks","Replication issues require attention to maintain fault tolerance"</t>
-  </si>
-  <si>
-    <t>19,"What is the HDFS read and write throughput? Calculate average throughput by storage type.","Throughput Analysis","Group by Storage_Type; average Read/Write Throughput","SSD: Read 475 MBps, Write 365 MBps; HDD: Read 255 MBps, Write 190 MBps. SSD is 1.9x faster","Storage type selection impacts analytics performance"</t>
-  </si>
-  <si>
-    <t>20,"Create an HDFS cluster summary with key metrics: total storage, used storage, replication overhead, cluster health.","Cluster Summary","Calculate summary metrics","Total Raw: 34,816 MB; Actual Storage: 104,448 MB (3x replication); Used: 62,669 MB (60%); Overhead: 69,632 MB; Health: 95.2%","HDFS provides scalable, fault-tolerant storage with replication overhead"</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -199,33 +39,86 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -423,285 +316,968 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B51"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Row_ID,Order_ID,Product_Name,Category,Status,Return_Flag,Region_Code,Payment_Method,Shipping_Mode,Discount_Rate,Discount_Text,Sales_Amount,Quantity,Profit,Notes,Date_Recorded,Customer_Type,Priority,Size,Color,Rating</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>1,ORD-1001,MacBook Pro,Electronics,Active,N,NW,Credit Card,Standard,0.05,5%,1299.99,1,389.99,Excellent customer,2024-01-05,Corporate,High,Large,Silver,5</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>2,ORD-1002,Magic Mouse,Electronics,Active,N,NW,PayPal,Express,0.10,10%,79.99,3,23.99,,2024-01-05,Corporate,Medium,Small,White,4</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>3,ORD-1003,Designer Jeans,Clothing,Active,N,SW,Debit Card,Standard,0.00,0%,89.99,2,26.99,First time customer,2024-01-06,Consumer,Medium,Medium,Blue,4</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>4,ORD-1004,27-inch Monitor,Electronics,Active,N,SW,Credit Card,Express,0.15,15%,299.99,1,89.99,,2024-01-06,Consumer,High,Large,Black,5</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>5,ORD-1005,Executive Chair,Furniture,Active,N,NE,Credit Card,Standard,0.05,5%,399.99,2,119.99,VIP customer,2024-01-07,Corporate,High,Large,Black,5</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>6,ORD-1006,Mechanical Keyboard,Electronics,Delayed,N,NE,PayPal,Standard,0.10,10%,89.99,2,26.99,,2024-01-07,Consumer,Medium,Medium,RGB,4</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>7,ORD-1007,Leather Jacket,Clothing,Active,N,WC,Debit Card,Express,0.20,20%,199.99,1,59.99,,2024-01-08,Home Office,High,Medium,Black,5</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>8,ORD-1008,iPad,Electronics,Active,N,WC,Credit Card,Standard,0.05,5%,499.99,1,149.99,,2024-01-08,Corporate,High,Medium,Space Gray,5</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>9,ORD-1009,Floor Lamp,Furniture,Active,N,NW,PayPal,Standard,0.00,0%,79.99,2,23.99,,2024-01-09,Consumer,Low,Medium,Black,3</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>10,ORD-1010,Running Shoes,Clothing,Returned,Y,NW,Debit Card,Express,0.10,10%,69.99,1,20.99,Size issue,2024-01-09,Consumer,Medium,Small,Blue,2</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>11,ORD-1011,Gaming Laptop,Electronics,Active,N,SW,Credit Card,Standard,0.15,15%,1299.99,1,389.99,,2024-01-10,Corporate,High,Large,Black,5</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>12</v>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12,ORD-1012,Headphones,Electronics,Active,N,NE,PayPal,Express,0.05,5%,149.99,2,44.99,,2024-01-10,Consumer,Medium,Medium,Black,4</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>13,ORD-1013,Wool Coat,Clothing,Active,N,WC,Debit Card,Standard,0.20,20%,189.99,1,56.99,,2024-01-11,Home Office,High,Large,Camel,5</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>14</v>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>14,ORD-1014,Bookshelf,Furniture,Active,N,NW,Credit Card,Standard,0.10,10%,159.99,1,47.99,,2024-01-11,Corporate,Medium,Large,Oak,4</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
-        <v>15</v>
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>15,ORD-1015,Smartphone,Electronics,Active,N,SW,Credit Card,Express,0.05,5%,699.99,2,209.99,,2024-01-12,Consumer,High,Medium,Black,5</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>16</v>
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>16,ORD-1016,Dress Shirt,Clothing,Active,N,NE,PayPal,Standard,0.00,0%,59.99,3,17.99,,2024-01-12,Corporate,Medium,Medium,White,4</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
-        <v>17</v>
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>17,ORD-1017,External SSD,Electronics,Active,N,WC,Debit Card,Standard,0.10,10%,99.99,1,29.99,,2024-01-13,Consumer,Low,Small,Black,4</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
-        <v>18</v>
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>18,ORD-1018,Hoodie,Clothing,Returned,Y,NW,PayPal,Express,0.05,5%,49.99,2,14.99,Wrong size,2024-01-13,Consumer,Medium,Medium,Gray,2</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
-        <v>19</v>
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>19,ORD-1019,Gaming Desk,Furniture,Active,N,SW,Credit Card,Standard,0.15,15%,349.99,1,104.99,,2024-01-14,Corporate,High,Large,Black,5</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="s">
-        <v>20</v>
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>20,ORD-1020,Webcam,Electronics,Active,N,NE,PayPal,Express,0.10,10%,79.99,2,23.99,,2024-01-14,Home Office,Medium,Small,Black,4</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="s">
-        <v>21</v>
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>21,ORD-1021,Docking Station,Electronics,Active,N,WC,Debit Card,Standard,0.00,0%,129.99,1,38.99,,2024-02-01,Consumer,Medium,Medium,Silver,4</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="s">
-        <v>22</v>
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>22,ORD-1022,Winter Parka,Clothing,Active,N,NW,Credit Card,Standard,0.05,5%,179.99,1,53.99,,2024-02-01,Consumer,High,Large,Navy,5</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="s">
-        <v>23</v>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>23,ORD-1023,Office Desk,Furniture,Active,N,SW,PayPal,Express,0.10,10%,449.99,1,134.99,,2024-02-02,Corporate,High,Large,Oak,5</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="s">
-        <v>24</v>
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>24,ORD-1024,USB-C Hub,Electronics,Active,N,NE,Debit Card,Standard,0.00,0%,39.99,3,11.99,,2024-02-02,Consumer,Low,Small,Silver,3</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="s">
-        <v>25</v>
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>25,ORD-1025,Casual Blazer,Clothing,Active,N,WC,Credit Card,Express,0.15,15%,149.99,1,44.99,,2024-02-03,Home Office,Medium,Medium,Navy,4</t>
+        </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="s">
-        <v>26</v>
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>26,ORD-1026,Gaming Mouse,Electronics,Returned,Y,NW,PayPal,Standard,0.10,10%,59.99,2,17.99,Defective product,2024-02-03,Consumer,Medium,Small,RGB,2</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="s">
-        <v>27</v>
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>27,ORD-1027,Laser Printer,Electronics,Active,N,SW,Debit Card,Standard,0.05,5%,199.99,1,59.99,,2024-02-04,Corporate,High,Large,White,5</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="s">
-        <v>28</v>
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>28,ORD-1028,Lounge Chair,Furniture,Active,N,NE,Credit Card,Standard,0.20,20%,279.99,1,83.99,,2024-02-04,Consumer,High,Large,Brown,5</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="s">
-        <v>29</v>
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>29,ORD-1029,Power Bank,Electronics,Active,N,WC,PayPal,Express,0.00,0%,49.99,4,14.99,,2024-02-05,Consumer,Low,Small,Black,4</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="s">
-        <v>30</v>
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>30,ORD-1030,Wool Scarf,Clothing,Active,N,NW,Debit Card,Standard,0.10,10%,24.99,5,7.49,,2024-02-05,Consumer,Low,Small,Gray,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>31,ORD-1031,Gaming Headset,Electronics,Active,N,SW,Credit Card,Express,0.05,5%,119.99,1,35.99,,2024-02-06,Corporate,Medium,Medium,Black,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>32,ORD-1032,Night Stand,Furniture,Active,N,NE,PayPal,Standard,0.10,10%,69.99,2,20.99,,2024-02-06,Home Office,Medium,Medium,Oak,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>33,ORD-1033,Athletic Shoes,Clothing,Active,N,WC,Debit Card,Standard,0.15,15%,109.99,1,32.99,,2024-02-07,Consumer,Medium,Medium,Blue,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>34,ORD-1034,Smart Watch,Electronics,Active,N,NW,Credit Card,Express,0.05,5%,199.99,1,59.99,,2024-02-07,Consumer,High,Small,Black,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>35,ORD-1035,Bluetooth Speaker,Electronics,Active,N,SW,PayPal,Standard,0.10,10%,79.99,2,23.99,,2024-02-08,Corporate,Medium,Small,Red,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>36,ORD-1036,Cashmere Sweater,Clothing,Returned,Y,NE,Debit Card,Standard,0.00,0%,99.99,1,29.99,Quality issue,2024-02-08,Consumer,Medium,Medium,Cream,2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>37,ORD-1037,Bookshelf,Furniture,Active,N,WC,Credit Card,Express,0.05,5%,129.99,1,38.99,,2024-02-09,Home Office,Medium,Large,White,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>38,ORD-1038,Mesh Router,Electronics,Active,N,NW,PayPal,Standard,0.10,10%,99.99,1,29.99,,2024-02-09,Consumer,Medium,Medium,White,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>39,ORD-1039,Golf Polo,Clothing,Active,N,SW,Debit Card,Standard,0.15,15%,44.99,3,13.49,,2024-02-10,Consumer,Low,Medium,Blue,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>40,ORD-1040,Graphics Card,Electronics,Active,N,WC,Credit Card,Express,0.20,20%,499.99,1,149.99,,2024-02-10,Corporate,High,Medium,Black,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>41,ORD-1041,Desktop PC,Electronics,Active,N,NW,PayPal,Standard,0.05,5%,999.99,1,299.99,,2024-03-01,Corporate,High,Large,Black,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>42,ORD-1042,Yoga Pants,Clothing,Active,N,SW,Debit Card,Express,0.00,0%,49.99,2,14.99,,2024-03-01,Consumer,Medium,Medium,Black,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>43,ORD-1043,Coffee Table,Furniture,Active,N,NE,Credit Card,Standard,0.10,10%,249.99,1,74.99,,2024-03-02,Corporate,High,Large,Oak,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>44,ORD-1044,Smart Speaker,Electronics,Active,N,WC,PayPal,Express,0.00,0%,89.99,2,26.99,,2024-03-02,Home Office,Medium,Medium,Black,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>45,ORD-1045,Baseball Cap,Clothing,Active,N,NW,Debit Card,Standard,0.05,5%,19.99,4,5.99,,2024-03-03,Consumer,Low,Small,Navy,3</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>46,ORD-1046,Quadcopter,Electronics,Active,N,SW,Credit Card,Express,0.10,10%,349.99,1,104.99,,2024-03-03,Consumer,High,Medium,Black,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>47,ORD-1047,Wall Mirror,Furniture,Active,N,NE,PayPal,Standard,0.00,0%,59.99,2,17.99,,2024-03-04,Consumer,Medium,Large,Silver,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>48,ORD-1048,Flannel Shirt,Clothing,Active,N,WC,Debit Card,Standard,0.10,10%,49.99,2,14.99,,2024-03-04,Home Office,Medium,Medium,Red,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>49,ORD-1049,Streaming Stick,Electronics,Returned,Y,NW,Credit Card,Standard,0.05,5%,29.99,3,8.99,Not working properly,2024-03-05,Consumer,Low,Small,Black,2</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>50,ORD-1050,Leggings,Clothing,Active,N,SW,PayPal,Express,0.00,0%,29.99,4,8.99,,2024-03-05,Consumer,Medium,Small,Black,4</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>31</v>
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>Replace all null/blank values in the 'Notes' column with 'No notes'. How many replacements were made?</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr"/>
+      <c r="F2" s="0" t="inlineStr"/>
+      <c r="G2" s="0" t="inlineStr"/>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>Replace all 'N' values in the 'Return_Flag' column with 'No' and 'Y' with 'Yes'.</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr"/>
+      <c r="F3" s="0" t="inlineStr"/>
+      <c r="G3" s="0" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
+      <c r="I3" s="0" t="inlineStr"/>
+      <c r="J3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>Replace all 'Active' values in 'Status' column with 'Active Order' and 'Delayed' with 'Delayed Order' and 'Returned' with 'Returned Order'.</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr"/>
+      <c r="F4" s="0" t="inlineStr"/>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>Replace all blank/null values in 'Rating' column with the average rating (4.2). How many blanks were replaced?</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr"/>
+      <c r="F5" s="0" t="inlineStr"/>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>Replace all 'Corporate' values in 'Customer_Type' column with 'Business' and 'Consumer' with 'Individual' and 'Home Office' with 'Home'.</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr"/>
+      <c r="F6" s="0" t="inlineStr"/>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="A7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>Replace all 'Black' colors in 'Color' column with 'Dark' and 'White' with 'Light'. How many replacements were made?</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr"/>
+      <c r="F7" s="0" t="inlineStr"/>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="A8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>Replace all 'High' priority values with 'High Priority' and 'Medium' with 'Standard Priority' and 'Low' with 'Low Priority'.</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr"/>
+      <c r="F8" s="0" t="inlineStr"/>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="A9" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>Replace all 'Large' size values with 'L' and 'Medium' with 'M' and 'Small' with 'S'.</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr"/>
+      <c r="F9" s="0" t="inlineStr"/>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="A10" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>Replace all 'Electronics' category values with 'Tech' and 'Clothing' with 'Apparel'.</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr"/>
+      <c r="F10" s="0" t="inlineStr"/>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="A11" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>Replace all 'Credit Card' payment methods with 'CC' and 'PayPal' with 'PP' and 'Debit Card' with 'DC'.</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr"/>
+      <c r="F11" s="0" t="inlineStr"/>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="A12" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>Replace all 'Standard' shipping mode with 'Std' and 'Express' with 'Exp'.</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr"/>
+      <c r="F12" s="0" t="inlineStr"/>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="A13" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>Replace all 'NW' region codes with 'Northwest' and 'SW' with 'Southwest' and 'NE' with 'Northeast' and 'WC' with 'West Coast'.</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr"/>
+      <c r="F13" s="0" t="inlineStr"/>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="A14" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>Replace all discount values of 0.00 in 'Discount_Rate' column with 'No Discount' in a new text column.</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr"/>
+      <c r="F14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="A15" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Replace all '5' ratings in 'Rating' column with 'Excellent' and '4' with 'Good' and '3' with 'Average' and '2' with 'Poor'.</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr"/>
+      <c r="F15" s="0" t="inlineStr"/>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="A16" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>Replace all empty strings in 'Notes' column with 'No comments' and trim any leading/trailing spaces.</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr"/>
+      <c r="F16" s="0" t="inlineStr"/>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>47</v>
-      </c>
+      <c r="A17" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>Replace all instances of 'Black' color with 'Dark' and also replace 'Gray' with 'Dark' to consolidate dark colors.</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr"/>
+      <c r="F17" s="0" t="inlineStr"/>
+      <c r="G17" s="0" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="A18" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>Replace all null values in 'Priority' column with 'Standard Priority' and in 'Size' column with 'Standard Size'.</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr"/>
+      <c r="F18" s="0" t="inlineStr"/>
+      <c r="G18" s="0" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
-        <v>49</v>
-      </c>
+      <c r="A19" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>Replace all 'RGB' color values with 'Multi-Color' and 'Space Gray' with 'Gray' to standardize color naming.</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr"/>
+      <c r="F19" s="0" t="inlineStr"/>
+      <c r="G19" s="0" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="A20" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>Replace all text in 'Product_Name' column to proper case (first letter capital). Also replace any 'MacBook' with 'MacBook Pro' where applicable.</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr"/>
+      <c r="F20" s="0" t="inlineStr"/>
+      <c r="G20" s="0" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Replacing Values</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Replace all 'Unknown' or null values in 'Customer_Type' with 'Not Specified'. Also replace any blank values with 'Not Specified'.</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr"/>
+      <c r="F21" s="0" t="inlineStr"/>
+      <c r="G21" s="0" t="inlineStr"/>
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>